--- a/Manual calc.xlsx
+++ b/Manual calc.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6d20085048815992/Documenti/GitHub/ranking_aus_super/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="120" documentId="8_{6B50DBFC-E840-4F93-9C07-3F647D2188CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4B80A72-051B-40AD-A9F7-7FCB07C81203}"/>
+  <xr:revisionPtr revIDLastSave="467" documentId="8_{6B50DBFC-E840-4F93-9C07-3F647D2188CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79CA765E-30C6-41DF-B90F-D062F60B2017}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{463C025B-1AEA-4D48-A61E-6EBBD6EBE81E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{463C025B-1AEA-4D48-A61E-6EBBD6EBE81E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Calc" sheetId="1" r:id="rId1"/>
-    <sheet name="Sources" sheetId="2" r:id="rId2"/>
+    <sheet name="Sources" sheetId="2" r:id="rId1"/>
+    <sheet name="Calc" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="97">
   <si>
     <t>Balance:</t>
   </si>
@@ -130,6 +130,207 @@
   </si>
   <si>
     <t>https://www.bussq.com.au/superannuation/super-with-bussq/fees-and-costs</t>
+  </si>
+  <si>
+    <t>CareSuper</t>
+  </si>
+  <si>
+    <t>https://www.caresuper.com.au/members/why-choose-us/fees-and-costs</t>
+  </si>
+  <si>
+    <t>Balanced</t>
+  </si>
+  <si>
+    <t>https://www.brightersuper.com.au/compare/fees-and-costs</t>
+  </si>
+  <si>
+    <t>Brighter Super</t>
+  </si>
+  <si>
+    <t>MYSUPER</t>
+  </si>
+  <si>
+    <t>OneSuper</t>
+  </si>
+  <si>
+    <t>https://www.superguide.com.au/super-funds-guide/onesuper</t>
+  </si>
+  <si>
+    <t>https://www.smartmonday.com.au/tools-and-resources/forms-and-factsheets#pds-smartmonday-prime</t>
+  </si>
+  <si>
+    <t>Smart_Monday_1786595961-final_sm_pds_tesf_14082026.pdf</t>
+  </si>
+  <si>
+    <t>smartMonday LifeStage</t>
+  </si>
+  <si>
+    <t>https://www.firstsuper.com.au/superannuation/fees-costs/</t>
+  </si>
+  <si>
+    <t>FIRST Super</t>
+  </si>
+  <si>
+    <t>HESTA Super Fund</t>
+  </si>
+  <si>
+    <t>HOSTPLUS Superannuation Fund</t>
+  </si>
+  <si>
+    <t>HOSTPLUS_fees-and-costs-guide.pdf.coredownload.pdf</t>
+  </si>
+  <si>
+    <t>https://hostplus.com.au/about-us/legals/pds#accordion-f7de90f571-item-cd98b24680</t>
+  </si>
+  <si>
+    <t>IOOF MYSUPER</t>
+  </si>
+  <si>
+    <t>IOOF MYSUPER_mysuper-dashboard.pdf</t>
+  </si>
+  <si>
+    <t>https://www.ioof.com.au/superannuation/mysuper-dashboard</t>
+  </si>
+  <si>
+    <t>https://www.legalsuper.com.au/why-join-legalsuper/superannuation-fees?openAccordions=What-do-administration-fees-cover%3F</t>
+  </si>
+  <si>
+    <t>legalsuper</t>
+  </si>
+  <si>
+    <t>HighGrowth</t>
+  </si>
+  <si>
+    <t>Mercer SmartPath</t>
+  </si>
+  <si>
+    <t>Smart Super</t>
+  </si>
+  <si>
+    <t>MercerSmartSuper_PDS.pdf</t>
+  </si>
+  <si>
+    <t>https://www.mercersuper.com.au/documents/product-disclosure-statement/</t>
+  </si>
+  <si>
+    <t>https://www.amp.com.au/superannuation/amp-super/fees-and-costs</t>
+  </si>
+  <si>
+    <t>AMP MySuper Options</t>
+  </si>
+  <si>
+    <t>AMP MySuper Options_sge-pds.pdf</t>
+  </si>
+  <si>
+    <t>https://nesssuper.com.au/pds/</t>
+  </si>
+  <si>
+    <t>NESS Super</t>
+  </si>
+  <si>
+    <t>https://www.ngssuper.com.au/files/documents/fees-costs-and-tax.pdf</t>
+  </si>
+  <si>
+    <t>NGS Super</t>
+  </si>
+  <si>
+    <t>https://www.mlc.com.au/adviser/super/products/mlc-masterkey-super-fundamentals/fees</t>
+  </si>
+  <si>
+    <t>MLC Australia</t>
+  </si>
+  <si>
+    <t>MLC Balanced</t>
+  </si>
+  <si>
+    <t>Prime Super</t>
+  </si>
+  <si>
+    <t>https://primesuper.com.au/member/super/fees</t>
+  </si>
+  <si>
+    <t>REI Super</t>
+  </si>
+  <si>
+    <t>https://www.reisuper.com.au/home/how-super-works/our-fees-and-costs</t>
+  </si>
+  <si>
+    <t>rei-super-fees-and-costs.pdf</t>
+  </si>
+  <si>
+    <t>Rest Super</t>
+  </si>
+  <si>
+    <t>https://rest.com.au/super/products/fees-and-costs</t>
+  </si>
+  <si>
+    <t>Team Super </t>
+  </si>
+  <si>
+    <t>https://www.teamsuper.com/Members/super/super-explained/fees-and-taxes</t>
+  </si>
+  <si>
+    <t>https://www.equipsuper.com.au/your-super/fees-and-costs</t>
+  </si>
+  <si>
+    <t>Equipsuper</t>
+  </si>
+  <si>
+    <t>MySuper</t>
+  </si>
+  <si>
+    <t>Equisuper_myfuture-fees-and-other-costs.pdf</t>
+  </si>
+  <si>
+    <t>https://russellinvestments.com/content/ri/au/en-gb/member/superannuation/why-choose-us/iq-super-for-life.html</t>
+  </si>
+  <si>
+    <t>Russell Investments Master Trust_iq super for life.pdf</t>
+  </si>
+  <si>
+    <t>Russell Investments Master Trust</t>
+  </si>
+  <si>
+    <t>UniSuper</t>
+  </si>
+  <si>
+    <t>UniSuper_fees-and-costs.pdf</t>
+  </si>
+  <si>
+    <t>https://www.unisuper.com.au/super/fees-and-costs</t>
+  </si>
+  <si>
+    <t>Cbus Super</t>
+  </si>
+  <si>
+    <t>CBUS_fees.pdf</t>
+  </si>
+  <si>
+    <t>Growth</t>
+  </si>
+  <si>
+    <t>Vanguard MySuper</t>
+  </si>
+  <si>
+    <t>https://www.cbussuper.com.au/fees</t>
+  </si>
+  <si>
+    <t>https://www.vanguard.com.au/super/performance-and-fees/fees/superannuation</t>
+  </si>
+  <si>
+    <t>Lifecycle</t>
+  </si>
+  <si>
+    <t>Vision Active Super</t>
+  </si>
+  <si>
+    <t>https://www.visionsuper.com.au/forms-and-resources/pds</t>
+  </si>
+  <si>
+    <t>Active Super Saver Fees and costs additional guide.pdf</t>
+  </si>
+  <si>
+    <t>Active Super Saver</t>
   </si>
 </sst>
 </file>
@@ -138,9 +339,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -178,6 +379,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000F69"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -201,9 +408,9 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
@@ -211,6 +418,8 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -228,6 +437,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -546,251 +759,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12160F08-CD7F-42F2-8486-2D3F0ECC06EA}">
-  <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="24.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="6">
-        <f>52*1.1</f>
-        <v>57.2</v>
-      </c>
-      <c r="C5" s="6">
-        <f>52*1</f>
-        <v>52</v>
-      </c>
-      <c r="D5" s="6">
-        <v>60</v>
-      </c>
-      <c r="E5" s="6">
-        <v>60</v>
-      </c>
-      <c r="F5" s="6">
-        <f>52</f>
-        <v>52</v>
-      </c>
-      <c r="G5" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="2">
-        <f>B5/$B$2</f>
-        <v>3.8133333333333335E-4</v>
-      </c>
-      <c r="C6" s="2">
-        <f>C5/$B$2</f>
-        <v>3.4666666666666667E-4</v>
-      </c>
-      <c r="D6" s="2">
-        <f>D5/$B$2</f>
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="E6" s="2">
-        <f>E5/$B$2</f>
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F6" s="2">
-        <f>F5/$B$2</f>
-        <v>3.4666666666666667E-4</v>
-      </c>
-      <c r="G6" s="2">
-        <f>G5/$B$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="7">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="C7" s="7">
-        <v>1E-3</v>
-      </c>
-      <c r="D7" s="7">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="E7" s="7">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F7" s="7">
-        <v>1.6000000000000001E-3</v>
-      </c>
-      <c r="G7" s="7">
-        <v>1.8E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="4">
-        <f>B6+B7</f>
-        <v>9.8133333333333319E-4</v>
-      </c>
-      <c r="C8" s="4">
-        <f>C6+C7</f>
-        <v>1.3466666666666666E-3</v>
-      </c>
-      <c r="D8" s="4">
-        <f>D6+D7</f>
-        <v>7.4000000000000003E-3</v>
-      </c>
-      <c r="E8" s="4">
-        <f>E6+E7</f>
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="F8" s="4">
-        <f>F6+F7</f>
-        <v>1.9466666666666669E-3</v>
-      </c>
-      <c r="G8" s="4">
-        <f>G6+G7</f>
-        <v>1.8E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="8">
-        <v>3.8999999999999998E-3</v>
-      </c>
-      <c r="C10" s="8">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="D10" s="8">
-        <v>1.9900000000000001E-2</v>
-      </c>
-      <c r="E10" s="8">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="F10" s="8">
-        <v>4.4000000000000003E-3</v>
-      </c>
-      <c r="G10" s="8">
-        <v>6.4999999999999997E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="8">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="C11" s="8">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="D11" s="8">
-        <v>3.7000000000000002E-3</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0</v>
-      </c>
-      <c r="F11" s="8">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="G11" s="8">
-        <v>3.3E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="5">
-        <f>B8+B10+B11</f>
-        <v>5.3813333333333335E-3</v>
-      </c>
-      <c r="C13" s="5">
-        <f>C8+C10+C11</f>
-        <v>7.2466666666666669E-3</v>
-      </c>
-      <c r="D13" s="5">
-        <f>D8+D10+D11</f>
-        <v>3.1E-2</v>
-      </c>
-      <c r="E13" s="5">
-        <f>E8+E10+E11</f>
-        <v>6.8000000000000005E-3</v>
-      </c>
-      <c r="F13" s="5">
-        <f>F8+F10+F11</f>
-        <v>7.1466666666666675E-3</v>
-      </c>
-      <c r="G13" s="5">
-        <f>G8+G10+G11</f>
-        <v>1.1599999999999999E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90DF30D1-DF19-41B6-9365-5C237DAD46A5}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.26953125" bestFit="1" customWidth="1"/>
@@ -859,10 +829,1261 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>28</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12160F08-CD7F-42F2-8486-2D3F0ECC06EA}">
+  <dimension ref="A1:AQ15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1">
+        <v>150000</v>
+      </c>
+      <c r="D2" s="10"/>
+    </row>
+    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4" t="s">
+        <v>40</v>
+      </c>
+      <c r="L4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M4" t="s">
+        <v>43</v>
+      </c>
+      <c r="N4" t="s">
+        <v>44</v>
+      </c>
+      <c r="O4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>53</v>
+      </c>
+      <c r="R4" t="s">
+        <v>58</v>
+      </c>
+      <c r="S4" t="s">
+        <v>61</v>
+      </c>
+      <c r="T4" t="s">
+        <v>63</v>
+      </c>
+      <c r="U4" t="s">
+        <v>65</v>
+      </c>
+      <c r="V4" t="s">
+        <v>67</v>
+      </c>
+      <c r="W4" t="s">
+        <v>69</v>
+      </c>
+      <c r="X4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="6">
+        <f>52*1.1</f>
+        <v>57.2</v>
+      </c>
+      <c r="C5" s="6">
+        <f>52*1</f>
+        <v>52</v>
+      </c>
+      <c r="D5" s="6">
+        <v>60</v>
+      </c>
+      <c r="E5" s="6">
+        <v>60</v>
+      </c>
+      <c r="F5" s="6">
+        <f>52</f>
+        <v>52</v>
+      </c>
+      <c r="G5" s="6">
+        <f>0.5*52</f>
+        <v>26</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="J5" s="6">
+        <v>20</v>
+      </c>
+      <c r="K5" s="6">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="L5" s="6">
+        <f>1.65*52</f>
+        <v>85.8</v>
+      </c>
+      <c r="M5" s="6">
+        <v>52</v>
+      </c>
+      <c r="N5" s="6">
+        <v>78</v>
+      </c>
+      <c r="O5" s="6">
+        <v>78</v>
+      </c>
+      <c r="P5" s="6">
+        <f>0.99*52</f>
+        <v>51.48</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>0</v>
+      </c>
+      <c r="R5" s="6">
+        <f>1.5*52</f>
+        <v>78</v>
+      </c>
+      <c r="S5" s="6">
+        <f>1.4*52</f>
+        <v>72.8</v>
+      </c>
+      <c r="T5" s="6">
+        <v>65</v>
+      </c>
+      <c r="U5" s="6">
+        <f>1.15*52</f>
+        <v>59.8</v>
+      </c>
+      <c r="V5" s="6">
+        <f>1*52</f>
+        <v>52</v>
+      </c>
+      <c r="W5" s="6">
+        <v>0</v>
+      </c>
+      <c r="X5" s="6">
+        <v>78</v>
+      </c>
+      <c r="Y5" s="6">
+        <f>0.75*52</f>
+        <v>39</v>
+      </c>
+      <c r="Z5" s="6">
+        <v>52</v>
+      </c>
+      <c r="AA5" s="6">
+        <v>60</v>
+      </c>
+      <c r="AB5" s="6">
+        <v>96</v>
+      </c>
+      <c r="AC5" s="6">
+        <v>52</v>
+      </c>
+      <c r="AD5" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="6">
+        <f>1.27*52</f>
+        <v>66.040000000000006</v>
+      </c>
+      <c r="AF5" s="6"/>
+      <c r="AG5" s="6"/>
+      <c r="AH5" s="6"/>
+      <c r="AI5" s="6"/>
+      <c r="AJ5" s="6"/>
+      <c r="AK5" s="6"/>
+      <c r="AL5" s="6"/>
+      <c r="AM5" s="6"/>
+      <c r="AN5" s="6"/>
+      <c r="AO5" s="6"/>
+      <c r="AP5" s="6"/>
+      <c r="AQ5" s="6"/>
+    </row>
+    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2">
+        <f t="shared" ref="B6:G6" si="0">B5/$B$2</f>
+        <v>3.8133333333333335E-4</v>
+      </c>
+      <c r="C6" s="2">
+        <f t="shared" si="0"/>
+        <v>3.4666666666666667E-4</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="0"/>
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="E6" s="2">
+        <f t="shared" si="0"/>
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="F6" s="2">
+        <f t="shared" si="0"/>
+        <v>3.4666666666666667E-4</v>
+      </c>
+      <c r="G6" s="2">
+        <f t="shared" si="0"/>
+        <v>1.7333333333333334E-4</v>
+      </c>
+      <c r="H6" s="2">
+        <f>H5/$B$2</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <f>I5/$B$2</f>
+        <v>4.5066666666666665E-4</v>
+      </c>
+      <c r="J6" s="2">
+        <f>J5/$B$2</f>
+        <v>1.3333333333333334E-4</v>
+      </c>
+      <c r="K6" s="2">
+        <f>K5/$B$2</f>
+        <v>4.5066666666666665E-4</v>
+      </c>
+      <c r="L6" s="2">
+        <f>L5/$B$2</f>
+        <v>5.7200000000000003E-4</v>
+      </c>
+      <c r="M6" s="2">
+        <f>M5/$B$2</f>
+        <v>3.4666666666666667E-4</v>
+      </c>
+      <c r="N6" s="2">
+        <f>N5/$B$2</f>
+        <v>5.1999999999999995E-4</v>
+      </c>
+      <c r="O6" s="2">
+        <f>O5/$B$2</f>
+        <v>5.1999999999999995E-4</v>
+      </c>
+      <c r="P6" s="2">
+        <f t="shared" ref="P6:X6" si="1">P5/$B$2</f>
+        <v>3.4319999999999999E-4</v>
+      </c>
+      <c r="Q6" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R6" s="2">
+        <f t="shared" si="1"/>
+        <v>5.1999999999999995E-4</v>
+      </c>
+      <c r="S6" s="2">
+        <f t="shared" si="1"/>
+        <v>4.8533333333333333E-4</v>
+      </c>
+      <c r="T6" s="2">
+        <f t="shared" si="1"/>
+        <v>4.3333333333333331E-4</v>
+      </c>
+      <c r="U6" s="2">
+        <f t="shared" si="1"/>
+        <v>3.9866666666666664E-4</v>
+      </c>
+      <c r="V6" s="2">
+        <f t="shared" si="1"/>
+        <v>3.4666666666666667E-4</v>
+      </c>
+      <c r="W6" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X6" s="2">
+        <f>X5/$B$2</f>
+        <v>5.1999999999999995E-4</v>
+      </c>
+      <c r="Y6" s="2">
+        <f>Y5/$B$2</f>
+        <v>2.5999999999999998E-4</v>
+      </c>
+      <c r="Z6" s="2">
+        <f>Z5/$B$2</f>
+        <v>3.4666666666666667E-4</v>
+      </c>
+      <c r="AA6" s="2">
+        <f>AA5/$B$2</f>
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="AB6" s="2">
+        <f>AB5/$B$2</f>
+        <v>6.4000000000000005E-4</v>
+      </c>
+      <c r="AC6" s="2">
+        <f>AC5/$B$2</f>
+        <v>3.4666666666666667E-4</v>
+      </c>
+      <c r="AD6" s="2">
+        <f>AD5/$B$2</f>
+        <v>0</v>
+      </c>
+      <c r="AE6" s="2">
+        <f>AE5/$B$2</f>
+        <v>4.4026666666666672E-4</v>
+      </c>
+      <c r="AF6" s="2"/>
+      <c r="AG6" s="2"/>
+      <c r="AH6" s="2"/>
+      <c r="AI6" s="2"/>
+      <c r="AJ6" s="2"/>
+      <c r="AK6" s="2"/>
+      <c r="AL6" s="2"/>
+      <c r="AM6" s="2"/>
+      <c r="AN6" s="2"/>
+      <c r="AO6" s="2"/>
+      <c r="AP6" s="2"/>
+      <c r="AQ6" s="2"/>
+    </row>
+    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="7">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="C7" s="7">
+        <v>1E-3</v>
+      </c>
+      <c r="D7" s="7">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="E7" s="7">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="F7" s="7">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="G7" s="7">
+        <v>1.4E-3</v>
+      </c>
+      <c r="H7" s="7">
+        <v>1.8E-3</v>
+      </c>
+      <c r="I7" s="7">
+        <v>1.5E-3</v>
+      </c>
+      <c r="J7" s="7">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="K7" s="7">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="L7" s="7">
+        <v>1.8E-3</v>
+      </c>
+      <c r="M7" s="7">
+        <v>1.5E-3</v>
+      </c>
+      <c r="N7" s="7">
+        <v>0</v>
+      </c>
+      <c r="O7" s="7">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="P7" s="7">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>1.8E-3</v>
+      </c>
+      <c r="R7" s="7">
+        <v>1.9E-3</v>
+      </c>
+      <c r="S7" s="7">
+        <v>1.2750000000000001E-3</v>
+      </c>
+      <c r="T7" s="7">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="U7" s="7">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="V7" s="7">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="W7" s="7">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="X7" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="Y7" s="7">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="Z7" s="7">
+        <v>1.9E-3</v>
+      </c>
+      <c r="AA7" s="7">
+        <v>1.9E-3</v>
+      </c>
+      <c r="AB7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="7">
+        <v>1.9E-3</v>
+      </c>
+      <c r="AD7" s="7">
+        <v>3.3E-3</v>
+      </c>
+      <c r="AE7" s="7">
+        <v>1.4E-3</v>
+      </c>
+      <c r="AF7" s="7"/>
+      <c r="AG7" s="7"/>
+      <c r="AH7" s="7"/>
+      <c r="AI7" s="7"/>
+      <c r="AJ7" s="7"/>
+      <c r="AK7" s="7"/>
+      <c r="AL7" s="7"/>
+      <c r="AM7" s="7"/>
+      <c r="AN7" s="7"/>
+      <c r="AO7" s="7"/>
+      <c r="AP7" s="7"/>
+      <c r="AQ7" s="7"/>
+    </row>
+    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="4">
+        <f t="shared" ref="B8:G8" si="2">B6+B7</f>
+        <v>9.8133333333333319E-4</v>
+      </c>
+      <c r="C8" s="4">
+        <f t="shared" si="2"/>
+        <v>1.3466666666666666E-3</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="2"/>
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="E8" s="4">
+        <f t="shared" si="2"/>
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="F8" s="4">
+        <f t="shared" si="2"/>
+        <v>1.9466666666666669E-3</v>
+      </c>
+      <c r="G8" s="4">
+        <f t="shared" si="2"/>
+        <v>1.5733333333333333E-3</v>
+      </c>
+      <c r="H8" s="4">
+        <f>H6+H7</f>
+        <v>1.8E-3</v>
+      </c>
+      <c r="I8" s="4">
+        <f>I6+I7</f>
+        <v>1.9506666666666667E-3</v>
+      </c>
+      <c r="J8" s="4">
+        <f>J6+J7</f>
+        <v>3.6333333333333335E-3</v>
+      </c>
+      <c r="K8" s="4">
+        <f>K6+K7</f>
+        <v>2.0506666666666668E-3</v>
+      </c>
+      <c r="L8" s="4">
+        <f>L6+L7</f>
+        <v>2.372E-3</v>
+      </c>
+      <c r="M8" s="4">
+        <f>M6+M7</f>
+        <v>1.8466666666666666E-3</v>
+      </c>
+      <c r="N8" s="4">
+        <f>N6+N7</f>
+        <v>5.1999999999999995E-4</v>
+      </c>
+      <c r="O8" s="4">
+        <f>O6+O7</f>
+        <v>3.0200000000000001E-3</v>
+      </c>
+      <c r="P8" s="4">
+        <f t="shared" ref="P8:W8" si="3">P6+P7</f>
+        <v>3.2431999999999999E-3</v>
+      </c>
+      <c r="Q8" s="4">
+        <f t="shared" si="3"/>
+        <v>1.8E-3</v>
+      </c>
+      <c r="R8" s="4">
+        <f t="shared" si="3"/>
+        <v>2.4199999999999998E-3</v>
+      </c>
+      <c r="S8" s="4">
+        <f t="shared" si="3"/>
+        <v>1.7603333333333334E-3</v>
+      </c>
+      <c r="T8" s="4">
+        <f t="shared" si="3"/>
+        <v>2.1333333333333334E-3</v>
+      </c>
+      <c r="U8" s="4">
+        <f t="shared" si="3"/>
+        <v>1.5986666666666666E-3</v>
+      </c>
+      <c r="V8" s="4">
+        <f t="shared" si="3"/>
+        <v>2.8466666666666666E-3</v>
+      </c>
+      <c r="W8" s="4">
+        <f t="shared" si="3"/>
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="X8" s="4">
+        <f>X6+X7</f>
+        <v>1.5200000000000001E-3</v>
+      </c>
+      <c r="Y8" s="4">
+        <f>Y6+Y7</f>
+        <v>1.8600000000000001E-3</v>
+      </c>
+      <c r="Z8" s="4">
+        <f>Z6+Z7</f>
+        <v>2.2466666666666668E-3</v>
+      </c>
+      <c r="AA8" s="4">
+        <f>AA6+AA7</f>
+        <v>2.3E-3</v>
+      </c>
+      <c r="AB8" s="4">
+        <f>AB6+AB7</f>
+        <v>6.4000000000000005E-4</v>
+      </c>
+      <c r="AC8" s="4">
+        <f>AC6+AC7</f>
+        <v>2.2466666666666668E-3</v>
+      </c>
+      <c r="AD8" s="4">
+        <f>AD6+AD7</f>
+        <v>3.3E-3</v>
+      </c>
+      <c r="AE8" s="4">
+        <f>AE6+AE7</f>
+        <v>1.8402666666666667E-3</v>
+      </c>
+      <c r="AF8" s="4"/>
+      <c r="AG8" s="4"/>
+      <c r="AH8" s="4"/>
+      <c r="AI8" s="4"/>
+      <c r="AJ8" s="4"/>
+      <c r="AK8" s="4"/>
+      <c r="AL8" s="4"/>
+      <c r="AM8" s="4"/>
+      <c r="AN8" s="4"/>
+      <c r="AO8" s="4"/>
+      <c r="AP8" s="4"/>
+      <c r="AQ8" s="4"/>
+    </row>
+    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="8">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="C10" s="8">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="D10" s="8">
+        <v>6.1000000000000004E-3</v>
+      </c>
+      <c r="E10" s="8">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="F10" s="8">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="G10" s="8">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="H10" s="8">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="I10" s="8">
+        <v>4.7999999999999996E-3</v>
+      </c>
+      <c r="J10" s="8">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="K10" s="8">
+        <v>4.6800000000000001E-3</v>
+      </c>
+      <c r="L10" s="8">
+        <v>4.3E-3</v>
+      </c>
+      <c r="M10" s="8">
+        <v>4.7999999999999996E-3</v>
+      </c>
+      <c r="N10" s="8">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="O10" s="8">
+        <v>6.1000000000000004E-3</v>
+      </c>
+      <c r="P10" s="8">
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="R10" s="8">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="S10" s="8">
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="T10" s="8">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="U10" s="8">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="V10" s="8">
+        <v>3.8E-3</v>
+      </c>
+      <c r="W10" s="8">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="X10" s="8">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="Y10" s="8">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="Z10" s="8">
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="AA10" s="8">
+        <v>6.1999999999999998E-3</v>
+      </c>
+      <c r="AB10" s="8">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="AC10" s="8">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="AD10" s="8">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="AE10" s="8">
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="AF10" s="8"/>
+      <c r="AG10" s="8"/>
+      <c r="AH10" s="8"/>
+      <c r="AI10" s="8"/>
+      <c r="AJ10" s="8"/>
+      <c r="AK10" s="8"/>
+      <c r="AL10" s="8"/>
+      <c r="AM10" s="8"/>
+      <c r="AN10" s="8"/>
+      <c r="AO10" s="8"/>
+      <c r="AP10" s="8"/>
+      <c r="AQ10" s="8"/>
+    </row>
+    <row r="11" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="8">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="C11" s="8">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="D11" s="8">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0</v>
+      </c>
+      <c r="F11" s="8">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="G11" s="8">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="H11" s="8">
+        <v>3.3E-3</v>
+      </c>
+      <c r="I11" s="8">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="J11" s="8">
+        <v>0</v>
+      </c>
+      <c r="K11" s="8">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="L11" s="8">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="M11" s="8">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="N11" s="8">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="O11" s="8">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="P11" s="8">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="R11" s="8">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="S11" s="8">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="T11" s="8">
+        <v>1.4E-3</v>
+      </c>
+      <c r="U11" s="8">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="V11" s="8">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="W11" s="8">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="X11" s="8">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Y11" s="8">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Z11" s="8">
+        <v>1.4E-3</v>
+      </c>
+      <c r="AA11" s="8">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="AB11" s="8">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="AC11" s="8">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="AD11" s="8">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="AE11" s="8">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="AF11" s="8"/>
+      <c r="AG11" s="8"/>
+      <c r="AH11" s="8"/>
+      <c r="AI11" s="8"/>
+      <c r="AJ11" s="8"/>
+      <c r="AK11" s="8"/>
+      <c r="AL11" s="8"/>
+      <c r="AM11" s="8"/>
+      <c r="AN11" s="8"/>
+      <c r="AO11" s="8"/>
+      <c r="AP11" s="8"/>
+      <c r="AQ11" s="8"/>
+    </row>
+    <row r="13" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="5">
+        <f t="shared" ref="B13:G13" si="4">B8+B10+B11</f>
+        <v>5.3813333333333335E-3</v>
+      </c>
+      <c r="C13" s="5">
+        <f t="shared" si="4"/>
+        <v>7.2466666666666669E-3</v>
+      </c>
+      <c r="D13" s="5">
+        <f t="shared" si="4"/>
+        <v>1.0600000000000002E-2</v>
+      </c>
+      <c r="E13" s="5">
+        <f t="shared" si="4"/>
+        <v>6.8000000000000005E-3</v>
+      </c>
+      <c r="F13" s="5">
+        <f t="shared" si="4"/>
+        <v>7.1466666666666675E-3</v>
+      </c>
+      <c r="G13" s="5">
+        <f t="shared" si="4"/>
+        <v>6.5733333333333338E-3</v>
+      </c>
+      <c r="H13" s="5">
+        <f>H8+H10+H11</f>
+        <v>1.1599999999999999E-2</v>
+      </c>
+      <c r="I13" s="5">
+        <f>I8+I10+I11</f>
+        <v>7.4506666666666662E-3</v>
+      </c>
+      <c r="J13" s="5">
+        <f>J8+J10+J11</f>
+        <v>6.7333333333333334E-3</v>
+      </c>
+      <c r="K13" s="5">
+        <f>K8+K10+K11</f>
+        <v>7.0306666666666668E-3</v>
+      </c>
+      <c r="L13" s="5">
+        <f>L8+L10+L11</f>
+        <v>7.4720000000000003E-3</v>
+      </c>
+      <c r="M13" s="5">
+        <f>M8+M10+M11</f>
+        <v>7.0466666666666664E-3</v>
+      </c>
+      <c r="N13" s="5">
+        <f>N8+N10+N11</f>
+        <v>9.6200000000000001E-3</v>
+      </c>
+      <c r="O13" s="5">
+        <f>O8+O10+O11</f>
+        <v>9.92E-3</v>
+      </c>
+      <c r="P13" s="5">
+        <f>P8+P10+P11</f>
+        <v>9.3431999999999994E-3</v>
+      </c>
+      <c r="Q13" s="5">
+        <f>Q8+Q10+Q11</f>
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="R13" s="5">
+        <f>R8+R10+R11</f>
+        <v>6.5200000000000006E-3</v>
+      </c>
+      <c r="S13" s="5">
+        <f>S8+S10+S11</f>
+        <v>7.7603333333333335E-3</v>
+      </c>
+      <c r="T13" s="5">
+        <f>T8+T10+T11</f>
+        <v>1.2233333333333334E-2</v>
+      </c>
+      <c r="U13" s="5">
+        <f>U8+U10+U11</f>
+        <v>1.0398666666666667E-2</v>
+      </c>
+      <c r="V13" s="5">
+        <f>V8+V10+V11</f>
+        <v>7.7466666666666673E-3</v>
+      </c>
+      <c r="W13" s="5">
+        <f>W8+W10+W11</f>
+        <v>1.0500000000000001E-2</v>
+      </c>
+      <c r="X13" s="5">
+        <f>X8+X10+X11</f>
+        <v>6.4199999999999995E-3</v>
+      </c>
+      <c r="Y13" s="5">
+        <f>Y8+Y10+Y11</f>
+        <v>6.4599999999999996E-3</v>
+      </c>
+      <c r="Z13" s="5">
+        <f>Z8+Z10+Z11</f>
+        <v>8.8466666666666659E-3</v>
+      </c>
+      <c r="AA13" s="5">
+        <f>AA8+AA10+AA11</f>
+        <v>8.8999999999999999E-3</v>
+      </c>
+      <c r="AB13" s="5">
+        <f>AB8+AB10+AB11</f>
+        <v>5.1399999999999996E-3</v>
+      </c>
+      <c r="AC13" s="5">
+        <f>AC8+AC10+AC11</f>
+        <v>7.2466666666666669E-3</v>
+      </c>
+      <c r="AD13" s="5">
+        <f>AD8+AD10+AD11</f>
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="AE13" s="5">
+        <f>AE8+AE10+AE11</f>
+        <v>7.8402666666666666E-3</v>
+      </c>
+      <c r="AF13" s="5"/>
+      <c r="AG13" s="5"/>
+      <c r="AH13" s="5"/>
+      <c r="AI13" s="5"/>
+      <c r="AJ13" s="5"/>
+      <c r="AK13" s="5"/>
+      <c r="AL13" s="5"/>
+      <c r="AM13" s="5"/>
+      <c r="AN13" s="5"/>
+      <c r="AO13" s="5"/>
+      <c r="AP13" s="5"/>
+      <c r="AQ13" s="5"/>
+    </row>
+    <row r="14" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="P14" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>54</v>
+      </c>
+      <c r="U14" t="s">
+        <v>66</v>
+      </c>
+      <c r="V14" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>88</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Manual calc.xlsx
+++ b/Manual calc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6d20085048815992/Documenti/GitHub/ranking_aus_super/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="467" documentId="8_{6B50DBFC-E840-4F93-9C07-3F647D2188CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79CA765E-30C6-41DF-B90F-D062F60B2017}"/>
+  <xr:revisionPtr revIDLastSave="469" documentId="8_{6B50DBFC-E840-4F93-9C07-3F647D2188CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{821A9710-D872-4832-8638-DDDFBA467699}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{463C025B-1AEA-4D48-A61E-6EBBD6EBE81E}"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{463C025B-1AEA-4D48-A61E-6EBBD6EBE81E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sources" sheetId="2" r:id="rId1"/>
@@ -180,9 +180,6 @@
     <t>HOSTPLUS_fees-and-costs-guide.pdf.coredownload.pdf</t>
   </si>
   <si>
-    <t>https://hostplus.com.au/about-us/legals/pds#accordion-f7de90f571-item-cd98b24680</t>
-  </si>
-  <si>
     <t>IOOF MYSUPER</t>
   </si>
   <si>
@@ -331,6 +328,9 @@
   </si>
   <si>
     <t>Active Super Saver</t>
+  </si>
+  <si>
+    <t>https://www.hesta.com.au/members/your-superannuation/fees-and-costs</t>
   </si>
 </sst>
 </file>
@@ -883,10 +883,7 @@
         <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
@@ -896,168 +893,171 @@
       <c r="B14" t="s">
         <v>45</v>
       </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" t="s">
         <v>47</v>
-      </c>
-      <c r="B15" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" t="s">
         <v>58</v>
-      </c>
-      <c r="B18" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" t="s">
         <v>67</v>
-      </c>
-      <c r="B22" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" t="s">
         <v>69</v>
-      </c>
-      <c r="B23" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" t="s">
         <v>72</v>
-      </c>
-      <c r="B24" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" t="s">
         <v>74</v>
-      </c>
-      <c r="B25" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" t="s">
         <v>80</v>
-      </c>
-      <c r="C27" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" t="s">
         <v>83</v>
-      </c>
-      <c r="B28" t="s">
-        <v>85</v>
-      </c>
-      <c r="C28" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" t="s">
         <v>86</v>
-      </c>
-      <c r="B29" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" t="s">
         <v>93</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>94</v>
-      </c>
-      <c r="C31" t="s">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1138,55 +1138,55 @@
         <v>44</v>
       </c>
       <c r="O4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="U4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="V4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="W4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="X4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Z4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB4" t="s">
         <v>82</v>
       </c>
-      <c r="AB4" t="s">
-        <v>83</v>
-      </c>
       <c r="AC4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AD4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AE4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.35">
@@ -1337,99 +1337,99 @@
         <v>1.7333333333333334E-4</v>
       </c>
       <c r="H6" s="2">
-        <f>H5/$B$2</f>
+        <f t="shared" ref="H6:O6" si="1">H5/$B$2</f>
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <f>I5/$B$2</f>
+        <f t="shared" si="1"/>
         <v>4.5066666666666665E-4</v>
       </c>
       <c r="J6" s="2">
-        <f>J5/$B$2</f>
+        <f t="shared" si="1"/>
         <v>1.3333333333333334E-4</v>
       </c>
       <c r="K6" s="2">
-        <f>K5/$B$2</f>
+        <f t="shared" si="1"/>
         <v>4.5066666666666665E-4</v>
       </c>
       <c r="L6" s="2">
-        <f>L5/$B$2</f>
+        <f t="shared" si="1"/>
         <v>5.7200000000000003E-4</v>
       </c>
       <c r="M6" s="2">
-        <f>M5/$B$2</f>
+        <f t="shared" si="1"/>
         <v>3.4666666666666667E-4</v>
       </c>
       <c r="N6" s="2">
-        <f>N5/$B$2</f>
-        <v>5.1999999999999995E-4</v>
-      </c>
-      <c r="O6" s="2">
-        <f>O5/$B$2</f>
-        <v>5.1999999999999995E-4</v>
-      </c>
-      <c r="P6" s="2">
-        <f t="shared" ref="P6:X6" si="1">P5/$B$2</f>
-        <v>3.4319999999999999E-4</v>
-      </c>
-      <c r="Q6" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R6" s="2">
         <f t="shared" si="1"/>
         <v>5.1999999999999995E-4</v>
       </c>
+      <c r="O6" s="2">
+        <f t="shared" si="1"/>
+        <v>5.1999999999999995E-4</v>
+      </c>
+      <c r="P6" s="2">
+        <f t="shared" ref="P6:W6" si="2">P5/$B$2</f>
+        <v>3.4319999999999999E-4</v>
+      </c>
+      <c r="Q6" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R6" s="2">
+        <f t="shared" si="2"/>
+        <v>5.1999999999999995E-4</v>
+      </c>
       <c r="S6" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.8533333333333333E-4</v>
       </c>
       <c r="T6" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.3333333333333331E-4</v>
       </c>
       <c r="U6" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.9866666666666664E-4</v>
       </c>
       <c r="V6" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.4666666666666667E-4</v>
       </c>
       <c r="W6" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X6" s="2">
-        <f>X5/$B$2</f>
+        <f t="shared" ref="X6:AE6" si="3">X5/$B$2</f>
         <v>5.1999999999999995E-4</v>
       </c>
       <c r="Y6" s="2">
-        <f>Y5/$B$2</f>
+        <f t="shared" si="3"/>
         <v>2.5999999999999998E-4</v>
       </c>
       <c r="Z6" s="2">
-        <f>Z5/$B$2</f>
+        <f t="shared" si="3"/>
         <v>3.4666666666666667E-4</v>
       </c>
       <c r="AA6" s="2">
-        <f>AA5/$B$2</f>
+        <f t="shared" si="3"/>
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="AB6" s="2">
-        <f>AB5/$B$2</f>
+        <f t="shared" si="3"/>
         <v>6.4000000000000005E-4</v>
       </c>
       <c r="AC6" s="2">
-        <f>AC5/$B$2</f>
+        <f t="shared" si="3"/>
         <v>3.4666666666666667E-4</v>
       </c>
       <c r="AD6" s="2">
-        <f>AD5/$B$2</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE6" s="2">
-        <f>AE5/$B$2</f>
+        <f t="shared" si="3"/>
         <v>4.4026666666666672E-4</v>
       </c>
       <c r="AF6" s="2"/>
@@ -1557,123 +1557,123 @@
         <v>1</v>
       </c>
       <c r="B8" s="4">
-        <f t="shared" ref="B8:G8" si="2">B6+B7</f>
+        <f t="shared" ref="B8:G8" si="4">B6+B7</f>
         <v>9.8133333333333319E-4</v>
       </c>
       <c r="C8" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3466666666666666E-3</v>
       </c>
       <c r="D8" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="E8" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="F8" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.9466666666666669E-3</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.5733333333333333E-3</v>
       </c>
       <c r="H8" s="4">
-        <f>H6+H7</f>
+        <f t="shared" ref="H8:O8" si="5">H6+H7</f>
         <v>1.8E-3</v>
       </c>
       <c r="I8" s="4">
-        <f>I6+I7</f>
+        <f t="shared" si="5"/>
         <v>1.9506666666666667E-3</v>
       </c>
       <c r="J8" s="4">
-        <f>J6+J7</f>
+        <f t="shared" si="5"/>
         <v>3.6333333333333335E-3</v>
       </c>
       <c r="K8" s="4">
-        <f>K6+K7</f>
+        <f t="shared" si="5"/>
         <v>2.0506666666666668E-3</v>
       </c>
       <c r="L8" s="4">
-        <f>L6+L7</f>
+        <f t="shared" si="5"/>
         <v>2.372E-3</v>
       </c>
       <c r="M8" s="4">
-        <f>M6+M7</f>
+        <f t="shared" si="5"/>
         <v>1.8466666666666666E-3</v>
       </c>
       <c r="N8" s="4">
-        <f>N6+N7</f>
+        <f t="shared" si="5"/>
         <v>5.1999999999999995E-4</v>
       </c>
       <c r="O8" s="4">
-        <f>O6+O7</f>
+        <f t="shared" si="5"/>
         <v>3.0200000000000001E-3</v>
       </c>
       <c r="P8" s="4">
-        <f t="shared" ref="P8:W8" si="3">P6+P7</f>
+        <f t="shared" ref="P8:W8" si="6">P6+P7</f>
         <v>3.2431999999999999E-3</v>
       </c>
       <c r="Q8" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1.8E-3</v>
       </c>
       <c r="R8" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>2.4199999999999998E-3</v>
       </c>
       <c r="S8" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1.7603333333333334E-3</v>
       </c>
       <c r="T8" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>2.1333333333333334E-3</v>
       </c>
       <c r="U8" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1.5986666666666666E-3</v>
       </c>
       <c r="V8" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>2.8466666666666666E-3</v>
       </c>
       <c r="W8" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>2.5000000000000001E-3</v>
       </c>
       <c r="X8" s="4">
-        <f>X6+X7</f>
+        <f t="shared" ref="X8:AE8" si="7">X6+X7</f>
         <v>1.5200000000000001E-3</v>
       </c>
       <c r="Y8" s="4">
-        <f>Y6+Y7</f>
+        <f t="shared" si="7"/>
         <v>1.8600000000000001E-3</v>
       </c>
       <c r="Z8" s="4">
-        <f>Z6+Z7</f>
+        <f t="shared" si="7"/>
         <v>2.2466666666666668E-3</v>
       </c>
       <c r="AA8" s="4">
-        <f>AA6+AA7</f>
+        <f t="shared" si="7"/>
         <v>2.3E-3</v>
       </c>
       <c r="AB8" s="4">
-        <f>AB6+AB7</f>
+        <f t="shared" si="7"/>
         <v>6.4000000000000005E-4</v>
       </c>
       <c r="AC8" s="4">
-        <f>AC6+AC7</f>
+        <f t="shared" si="7"/>
         <v>2.2466666666666668E-3</v>
       </c>
       <c r="AD8" s="4">
-        <f>AD6+AD7</f>
+        <f t="shared" si="7"/>
         <v>3.3E-3</v>
       </c>
       <c r="AE8" s="4">
-        <f>AE6+AE7</f>
+        <f t="shared" si="7"/>
         <v>1.8402666666666667E-3</v>
       </c>
       <c r="AF8" s="4"/>
@@ -1908,123 +1908,123 @@
         <v>4</v>
       </c>
       <c r="B13" s="5">
-        <f t="shared" ref="B13:G13" si="4">B8+B10+B11</f>
+        <f t="shared" ref="B13:G13" si="8">B8+B10+B11</f>
         <v>5.3813333333333335E-3</v>
       </c>
       <c r="C13" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>7.2466666666666669E-3</v>
       </c>
       <c r="D13" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1.0600000000000002E-2</v>
       </c>
       <c r="E13" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>6.8000000000000005E-3</v>
       </c>
       <c r="F13" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>7.1466666666666675E-3</v>
       </c>
       <c r="G13" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>6.5733333333333338E-3</v>
       </c>
       <c r="H13" s="5">
-        <f>H8+H10+H11</f>
+        <f t="shared" ref="H13:AE13" si="9">H8+H10+H11</f>
         <v>1.1599999999999999E-2</v>
       </c>
       <c r="I13" s="5">
-        <f>I8+I10+I11</f>
+        <f t="shared" si="9"/>
         <v>7.4506666666666662E-3</v>
       </c>
       <c r="J13" s="5">
-        <f>J8+J10+J11</f>
+        <f t="shared" si="9"/>
         <v>6.7333333333333334E-3</v>
       </c>
       <c r="K13" s="5">
-        <f>K8+K10+K11</f>
+        <f t="shared" si="9"/>
         <v>7.0306666666666668E-3</v>
       </c>
       <c r="L13" s="5">
-        <f>L8+L10+L11</f>
+        <f t="shared" si="9"/>
         <v>7.4720000000000003E-3</v>
       </c>
       <c r="M13" s="5">
-        <f>M8+M10+M11</f>
+        <f t="shared" si="9"/>
         <v>7.0466666666666664E-3</v>
       </c>
       <c r="N13" s="5">
-        <f>N8+N10+N11</f>
+        <f t="shared" si="9"/>
         <v>9.6200000000000001E-3</v>
       </c>
       <c r="O13" s="5">
-        <f>O8+O10+O11</f>
+        <f t="shared" si="9"/>
         <v>9.92E-3</v>
       </c>
       <c r="P13" s="5">
-        <f>P8+P10+P11</f>
+        <f t="shared" si="9"/>
         <v>9.3431999999999994E-3</v>
       </c>
       <c r="Q13" s="5">
-        <f>Q8+Q10+Q11</f>
+        <f t="shared" si="9"/>
         <v>9.4000000000000004E-3</v>
       </c>
       <c r="R13" s="5">
-        <f>R8+R10+R11</f>
+        <f t="shared" si="9"/>
         <v>6.5200000000000006E-3</v>
       </c>
       <c r="S13" s="5">
-        <f>S8+S10+S11</f>
+        <f t="shared" si="9"/>
         <v>7.7603333333333335E-3</v>
       </c>
       <c r="T13" s="5">
-        <f>T8+T10+T11</f>
+        <f t="shared" si="9"/>
         <v>1.2233333333333334E-2</v>
       </c>
       <c r="U13" s="5">
-        <f>U8+U10+U11</f>
+        <f t="shared" si="9"/>
         <v>1.0398666666666667E-2</v>
       </c>
       <c r="V13" s="5">
-        <f>V8+V10+V11</f>
+        <f t="shared" si="9"/>
         <v>7.7466666666666673E-3</v>
       </c>
       <c r="W13" s="5">
-        <f>W8+W10+W11</f>
+        <f t="shared" si="9"/>
         <v>1.0500000000000001E-2</v>
       </c>
       <c r="X13" s="5">
-        <f>X8+X10+X11</f>
+        <f t="shared" si="9"/>
         <v>6.4199999999999995E-3</v>
       </c>
       <c r="Y13" s="5">
-        <f>Y8+Y10+Y11</f>
+        <f t="shared" si="9"/>
         <v>6.4599999999999996E-3</v>
       </c>
       <c r="Z13" s="5">
-        <f>Z8+Z10+Z11</f>
+        <f t="shared" si="9"/>
         <v>8.8466666666666659E-3</v>
       </c>
       <c r="AA13" s="5">
-        <f>AA8+AA10+AA11</f>
+        <f t="shared" si="9"/>
         <v>8.8999999999999999E-3</v>
       </c>
       <c r="AB13" s="5">
-        <f>AB8+AB10+AB11</f>
+        <f t="shared" si="9"/>
         <v>5.1399999999999996E-3</v>
       </c>
       <c r="AC13" s="5">
-        <f>AC8+AC10+AC11</f>
+        <f t="shared" si="9"/>
         <v>7.2466666666666669E-3</v>
       </c>
       <c r="AD13" s="5">
-        <f>AD8+AD10+AD11</f>
+        <f t="shared" si="9"/>
         <v>5.5999999999999999E-3</v>
       </c>
       <c r="AE13" s="5">
-        <f>AE8+AE10+AE11</f>
+        <f t="shared" si="9"/>
         <v>7.8402666666666666E-3</v>
       </c>
       <c r="AF13" s="5"/>
@@ -2042,28 +2042,28 @@
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.35">
       <c r="P14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="U14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AC14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AD14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.35">
@@ -2074,7 +2074,7 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E15" t="s">
         <v>25</v>
